--- a/tests/testdata/excel/ファイル名/ア_イ_ウ.xlsx
+++ b/tests/testdata/excel/ファイル名/ア_イ_ウ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{04096EA1-5914-4AED-80C8-605D818B09AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{44679385-511A-4AB4-8DA8-B4ED10893C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{DBFB3B13-64B1-469E-9CB1-4CF3C6583FED}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{E642ADA6-771B-46E9-87AC-6D290EF8F9DD}"/>
   </bookViews>
   <sheets>
     <sheet name="シ_ー_ト" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D9E5FF5-F4F9-4EBD-B751-496634030E77}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97C76A69-237F-4238-A9D5-459C92DBD5E8}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/tests/testdata/excel/ファイル名/ア_イ_ウ.xlsx
+++ b/tests/testdata/excel/ファイル名/ア_イ_ウ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{44679385-511A-4AB4-8DA8-B4ED10893C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DCAC82E-49B2-4C52-9153-76C27351C7BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{E642ADA6-771B-46E9-87AC-6D290EF8F9DD}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{14D0C57A-3399-4527-AC88-9ECC6C0E899C}"/>
   </bookViews>
   <sheets>
     <sheet name="シ_ー_ト" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97C76A69-237F-4238-A9D5-459C92DBD5E8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5D79283-9058-4AE2-840D-4E59047B41FC}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
